--- a/03 doc/Schwellwerte.xlsx
+++ b/03 doc/Schwellwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2f0ec7fd2bf0214/Desktop/Kurse/ML_Intro/03 doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1104" documentId="8_{F8DAB85A-692F-4C2F-BF0A-1B315DD8071C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5DD40EE-ECBE-4EBC-AF98-94B909AAB49F}"/>
+  <xr:revisionPtr revIDLastSave="1106" documentId="8_{F8DAB85A-692F-4C2F-BF0A-1B315DD8071C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A814712C-19D4-4841-8A1D-8E53CEF24C17}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D6461637-D3C8-44BF-9A86-6305C9AFE92E}"/>
   </bookViews>
@@ -332,12 +332,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -350,6 +344,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -359,10 +363,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Berechnung" xfId="3" builtinId="22"/>
@@ -400,6 +400,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -753,22 +757,22 @@
         <v>1</v>
       </c>
       <c r="E1" s="4">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="17"/>
+      <c r="M2" s="13"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -790,23 +794,23 @@
       <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <f>COUNTIFS(Tabelle1[Real],1,Tabelle1[Prognose],1)</f>
-        <v>20</v>
-      </c>
-      <c r="J4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>10</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="9">
         <f>TP</f>
-        <v>20</v>
-      </c>
-      <c r="M4" s="12">
+        <v>15</v>
+      </c>
+      <c r="M4" s="10">
         <f>FP</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -816,35 +820,35 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>0.3</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E5" s="1">
-        <f>IF(D5&gt;=$E$1,1,0)</f>
+        <f t="shared" ref="E5:E47" si="0">IF(D5&gt;=$E$1,1,0)</f>
         <v>1</v>
       </c>
       <c r="G5" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <f>COUNTIFS(Tabelle1[Real],0,Tabelle1[Prognose],0)</f>
-        <v>15</v>
-      </c>
-      <c r="J5" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="J5" s="16"/>
       <c r="K5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="10">
         <f>FN</f>
-        <v>3</v>
-      </c>
-      <c r="M5" s="11">
+        <v>8</v>
+      </c>
+      <c r="M5" s="9">
         <f>TN</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -854,25 +858,25 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>0.2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E6" s="1">
-        <f>IF(D6&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <f>COUNTIFS(Tabelle1[Real],0,Tabelle1[Prognose],1)</f>
-        <v>5</v>
-      </c>
-      <c r="J6" s="15"/>
+        <v>4</v>
+      </c>
+      <c r="J6" s="17"/>
       <c r="L6" t="s">
         <v>12</v>
       </c>
@@ -887,28 +891,28 @@
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>0.4</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.6</v>
       </c>
       <c r="E7" s="1">
-        <f>IF(D7&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <f>COUNTIFS(Tabelle1[Real],1,Tabelle1[Prognose],0)</f>
-        <v>3</v>
-      </c>
-      <c r="L7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="14"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -917,16 +921,16 @@
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>0.4</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.6</v>
       </c>
       <c r="E8" s="1">
-        <f>IF(D8&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -936,16 +940,16 @@
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>0.4</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.6</v>
       </c>
       <c r="E9" s="1">
-        <f>IF(D9&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -955,15 +959,15 @@
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>0.2</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E10" s="1">
-        <f>IF(D10&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -974,23 +978,23 @@
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>0.1</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.9</v>
       </c>
       <c r="E11" s="1">
-        <f>IF(D11&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <f>(TP+TN)/(TP+TN+FP+FN)</f>
-        <v>0.81395348837209303</v>
+        <v>0.72093023255813948</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -1000,23 +1004,23 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="7">
         <v>0.2</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E12" s="1">
-        <f>IF(D12&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <f>TP/(TP+FP)</f>
-        <v>0.8</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="P12" s="1"/>
     </row>
@@ -1027,23 +1031,23 @@
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>0.3</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E13" s="1">
-        <f>IF(D13&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="6">
         <f>TP/(TP+FN)</f>
-        <v>0.86956521739130432</v>
+        <v>0.65217391304347827</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -1053,23 +1057,23 @@
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>0.25</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.75</v>
       </c>
       <c r="E14" s="1">
-        <f>IF(D14&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="6">
         <f>2*(I12*I13)/(I12+I13)</f>
-        <v>0.83333333333333326</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -1079,16 +1083,16 @@
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>0.5</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.5</v>
       </c>
       <c r="E15" s="1">
-        <f>IF(D15&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -1098,15 +1102,15 @@
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <v>0.1</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.9</v>
       </c>
       <c r="E16" s="1">
-        <f>IF(D16&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1117,15 +1121,15 @@
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>0.2</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E17" s="1">
-        <f>IF(D17&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1136,15 +1140,15 @@
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="7">
         <v>0.3</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E18" s="1">
-        <f>IF(D18&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1155,15 +1159,15 @@
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="7">
         <v>0.25</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.75</v>
       </c>
       <c r="E19" s="1">
-        <f>IF(D19&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1174,15 +1178,15 @@
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="7">
         <v>0.1</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.9</v>
       </c>
       <c r="E20" s="1">
-        <f>IF(D20&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1193,15 +1197,15 @@
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>0.2</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E21" s="1">
-        <f>IF(D21&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1212,15 +1216,15 @@
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="7">
         <v>0.3</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E22" s="1">
-        <f>IF(D22&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1231,16 +1235,16 @@
       <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>0.4</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.6</v>
       </c>
       <c r="E23" s="1">
-        <f>IF(D23&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1250,15 +1254,15 @@
       <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="7">
         <v>0.3</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E24" s="1">
-        <f>IF(D24&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1269,15 +1273,15 @@
       <c r="B25" s="1">
         <v>0</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="7">
         <v>0.1</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.9</v>
       </c>
       <c r="E25" s="1">
-        <f>IF(D25&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1288,15 +1292,15 @@
       <c r="B26" s="1">
         <v>0</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="7">
         <v>0.2</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.8</v>
       </c>
       <c r="E26" s="1">
-        <f>IF(D26&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1307,15 +1311,15 @@
       <c r="B27" s="1">
         <v>0</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="7">
         <v>0.3</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.7</v>
       </c>
       <c r="E27" s="1">
-        <f>IF(D27&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1326,16 +1330,16 @@
       <c r="B28" s="1">
         <v>0</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="7">
         <v>0.4</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.6</v>
       </c>
       <c r="E28" s="1">
-        <f>IF(D28&gt;=$E$1,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1345,15 +1349,15 @@
       <c r="B29" s="1">
         <v>0</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="7">
         <v>0.1</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.9</v>
       </c>
       <c r="E29" s="1">
-        <f>IF(D29&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1364,15 +1368,15 @@
       <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="7">
         <v>0.9</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E30" s="1">
-        <f>IF(D30&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1383,15 +1387,15 @@
       <c r="B31" s="1">
         <v>1</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>0.8</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E31" s="1">
-        <f>IF(D31&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1402,15 +1406,15 @@
       <c r="B32" s="1">
         <v>0</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="7">
         <v>0.6</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.4</v>
       </c>
       <c r="E32" s="1">
-        <f>IF(D32&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1421,15 +1425,15 @@
       <c r="B33" s="1">
         <v>0</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E33" s="1">
-        <f>IF(D33&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1440,15 +1444,15 @@
       <c r="B34" s="1">
         <v>0</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="7">
         <v>0.51</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.49</v>
       </c>
       <c r="E34" s="1">
-        <f>IF(D34&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1459,15 +1463,15 @@
       <c r="B35" s="1">
         <v>0</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="7">
         <v>0.51</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.49</v>
       </c>
       <c r="E35" s="1">
-        <f>IF(D35&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1478,15 +1482,15 @@
       <c r="B36" s="1">
         <v>0</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.43999999999999995</v>
       </c>
       <c r="E36" s="1">
-        <f>IF(D36&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1497,15 +1501,15 @@
       <c r="B37" s="1">
         <v>0</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="7">
         <v>0.8</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E37" s="1">
-        <f>IF(D37&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1516,15 +1520,15 @@
       <c r="B38" s="1">
         <v>0</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="7">
         <v>0.9</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E38" s="1">
-        <f>IF(D38&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1535,15 +1539,15 @@
       <c r="B39" s="1">
         <v>0</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="7">
         <v>0.6</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.4</v>
       </c>
       <c r="E39" s="1">
-        <f>IF(D39&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1554,15 +1558,15 @@
       <c r="B40" s="1">
         <v>0</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="7">
         <v>0.7</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E40" s="1">
-        <f>IF(D40&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1573,15 +1577,15 @@
       <c r="B41" s="1">
         <v>0</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>0.8</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E41" s="1">
-        <f>IF(D41&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1592,15 +1596,15 @@
       <c r="B42" s="1">
         <v>0</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="7">
         <v>0.9</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E42" s="1">
-        <f>IF(D42&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1611,15 +1615,15 @@
       <c r="B43" s="1">
         <v>0</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="7">
         <v>0.6</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.4</v>
       </c>
       <c r="E43" s="1">
-        <f>IF(D43&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1630,15 +1634,15 @@
       <c r="B44" s="1">
         <v>0</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="7">
         <v>0.7</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E44" s="1">
-        <f>IF(D44&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1649,15 +1653,15 @@
       <c r="B45" s="1">
         <v>0</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="7">
         <v>0.8</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E45" s="1">
-        <f>IF(D45&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1668,15 +1672,15 @@
       <c r="B46" s="1">
         <v>0</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="7">
         <v>0.9</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E46" s="1">
-        <f>IF(D46&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1687,15 +1691,15 @@
       <c r="B47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="7">
         <v>0.6</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="7">
         <f>1-Tabelle1[[#This Row],[False]]</f>
         <v>0.4</v>
       </c>
       <c r="E47" s="1">
-        <f>IF(D47&gt;=$E$1,1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
